--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1838645935058594</v>
+        <v>0.19521164894104</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999313193305389</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2727642059326172</v>
+        <v>0.2581660747528076</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999407153367686</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1838645935058594</v>
+        <v>0.19521164894104</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999313193305389</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2727642059326172</v>
+        <v>0.2581660747528076</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999407153367686</v>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.19521164894104</v>
+        <v>1.398122549057007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999313193305389</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.999951176558577</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1376966291576827</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.076330175930234</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2581660747528076</v>
+        <v>1.773450374603271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999407153367686</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.999951176558577</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1376966291576827</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.076330175930234</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.19521164894104</v>
+        <v>1.398122549057007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999313193305389</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.999951176558577</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1376966291576827</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.076330175930234</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2581660747528076</v>
+        <v>1.773450374603271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999407153367686</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.999951176558577</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1376966291576827</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.076330175930234</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.398122549057007</v>
+        <v>3579.370558261871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.7104636535292844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8256278478515866</v>
       </c>
       <c r="G2" t="n">
-        <v>1.541436429431279</v>
+        <v>74.30724004700164</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9433131263880609</v>
+        <v>44.61004126385073</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.773450374603271</v>
+        <v>174.0478835105896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.994952709138001</v>
+        <v>0.7671612386426272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8256278478515866</v>
       </c>
       <c r="G3" t="n">
-        <v>1.541436429431279</v>
+        <v>74.30724004700164</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9433131263880609</v>
+        <v>44.61004126385073</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>294.8796832561493</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7948886129406575</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8256278478515866</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74.30724004700164</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44.61004126385073</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.398122549057007</v>
+        <v>3579.370558261871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.7104636535292844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8256278478515866</v>
       </c>
       <c r="G2" t="n">
-        <v>1.541436429431279</v>
+        <v>74.30724004700164</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9433131263880609</v>
+        <v>44.61004126385073</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.773450374603271</v>
+        <v>174.0478835105896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.994952709138001</v>
+        <v>0.7671612386426272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.8256278478515866</v>
       </c>
       <c r="G3" t="n">
-        <v>1.541436429431279</v>
+        <v>74.30724004700164</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9433131263880609</v>
+        <v>44.61004126385073</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>294.8796832561493</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7948886129406575</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8256278478515866</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74.30724004700164</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44.61004126385073</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3579.370558261871</v>
+        <v>0.7682609558105469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7104636535292844</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8256278478515866</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>74.30724004700164</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>44.61004126385073</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>174.0478835105896</v>
+        <v>1.033361673355103</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7671612386426272</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8256278478515866</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>74.30724004700164</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>44.61004126385073</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>294.8796832561493</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7948886129406575</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8256278478515866</v>
-      </c>
-      <c r="G4" t="n">
-        <v>74.30724004700164</v>
-      </c>
-      <c r="H4" t="n">
-        <v>44.61004126385073</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3579.370558261871</v>
+        <v>0.7682609558105469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7104636535292844</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8256278478515866</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>74.30724004700164</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>44.61004126385073</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>174.0478835105896</v>
+        <v>1.033361673355103</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7671612386426272</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8256278478515866</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>74.30724004700164</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>44.61004126385073</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>294.8796832561493</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7948886129406575</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8256278478515866</v>
-      </c>
-      <c r="G4" t="n">
-        <v>74.30724004700164</v>
-      </c>
-      <c r="H4" t="n">
-        <v>44.61004126385073</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7682609558105469</v>
+        <v>0.8011264801025391</v>
       </c>
       <c r="E2" t="n">
         <v>0.9907215425595718</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.033361673355103</v>
+        <v>0.9458091259002686</v>
       </c>
       <c r="E3" t="n">
         <v>0.994952709138001</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7682609558105469</v>
+        <v>0.8011264801025391</v>
       </c>
       <c r="E2" t="n">
         <v>0.9907215425595718</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.033361673355103</v>
+        <v>0.9458091259002686</v>
       </c>
       <c r="E3" t="n">
         <v>0.994952709138001</v>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8011264801025391</v>
+        <v>0.8370380401611328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.9845405056133624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.993079342099446</v>
       </c>
       <c r="G2" t="n">
-        <v>1.541436429431279</v>
+        <v>1.639391977685414</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9433131263880609</v>
+        <v>1.125017158355155</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9458091259002686</v>
+        <v>1.150445222854614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.994952709138001</v>
+        <v>0.9886933322688432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.993079342099446</v>
       </c>
       <c r="G3" t="n">
-        <v>1.541436429431279</v>
+        <v>1.639391977685414</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9433131263880609</v>
+        <v>1.125017158355155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8011264801025391</v>
+        <v>0.8370380401611328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.9845405056133624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.993079342099446</v>
       </c>
       <c r="G2" t="n">
-        <v>1.541436429431279</v>
+        <v>1.639391977685414</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9433131263880609</v>
+        <v>1.125017158355155</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9458091259002686</v>
+        <v>1.150445222854614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.994952709138001</v>
+        <v>0.9886933322688432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.993079342099446</v>
       </c>
       <c r="G3" t="n">
-        <v>1.541436429431279</v>
+        <v>1.639391977685414</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9433131263880609</v>
+        <v>1.125017158355155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8370380401611328</v>
+        <v>0.7700636386871338</v>
       </c>
       <c r="E2" t="n">
         <v>0.9845405056133624</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.150445222854614</v>
+        <v>1.345831871032715</v>
       </c>
       <c r="E3" t="n">
         <v>0.9886933322688432</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8370380401611328</v>
+        <v>0.7700636386871338</v>
       </c>
       <c r="E2" t="n">
         <v>0.9845405056133624</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.150445222854614</v>
+        <v>1.345831871032715</v>
       </c>
       <c r="E3" t="n">
         <v>0.9886933322688432</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7700636386871338</v>
+        <v>24.25910139083862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9845405056133624</v>
+        <v>0.5975161816596991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.993079342099446</v>
+        <v>0.6152384794986221</v>
       </c>
       <c r="G2" t="n">
-        <v>1.639391977685414</v>
+        <v>110.3794900020681</v>
       </c>
       <c r="H2" t="n">
-        <v>1.125017158355155</v>
+        <v>66.1107004478513</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.345831871032715</v>
+        <v>70.2791485786438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9886933322688432</v>
+        <v>0.6054362053095196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.993079342099446</v>
+        <v>0.6152384794986221</v>
       </c>
       <c r="G3" t="n">
-        <v>1.639391977685414</v>
+        <v>110.3794900020681</v>
       </c>
       <c r="H3" t="n">
-        <v>1.125017158355155</v>
+        <v>66.1107004478513</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7700636386871338</v>
+        <v>24.25910139083862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9845405056133624</v>
+        <v>0.5975161816596991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.993079342099446</v>
+        <v>0.6152384794986221</v>
       </c>
       <c r="G2" t="n">
-        <v>1.639391977685414</v>
+        <v>110.3794900020681</v>
       </c>
       <c r="H2" t="n">
-        <v>1.125017158355155</v>
+        <v>66.1107004478513</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.345831871032715</v>
+        <v>70.2791485786438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9886933322688432</v>
+        <v>0.6054362053095196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.993079342099446</v>
+        <v>0.6152384794986221</v>
       </c>
       <c r="G3" t="n">
-        <v>1.639391977685414</v>
+        <v>110.3794900020681</v>
       </c>
       <c r="H3" t="n">
-        <v>1.125017158355155</v>
+        <v>66.1107004478513</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>24.25910139083862</v>
+        <v>45.87179636955261</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5975161816596991</v>
+        <v>-0.5020893562381507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6152384794986221</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G2" t="n">
-        <v>110.3794900020681</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H2" t="n">
-        <v>66.1107004478513</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>70.2791485786438</v>
+        <v>80.76652526855469</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6054362053095196</v>
+        <v>-0.4289905192472201</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6152384794986221</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G3" t="n">
-        <v>110.3794900020681</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H3" t="n">
-        <v>66.1107004478513</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>24.25910139083862</v>
+        <v>45.87179636955261</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5975161816596991</v>
+        <v>-0.5020893562381507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6152384794986221</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G2" t="n">
-        <v>110.3794900020681</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H2" t="n">
-        <v>66.1107004478513</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>70.2791485786438</v>
+        <v>80.76652526855469</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6054362053095196</v>
+        <v>-0.4289905192472201</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6152384794986221</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G3" t="n">
-        <v>110.3794900020681</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H3" t="n">
-        <v>66.1107004478513</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>45.87179636955261</v>
+        <v>87.75858187675476</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5020893562381507</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.942240838910085</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5998887566777964</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.76652526855469</v>
+        <v>182.5361700057983</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4289905192472201</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.942240838910085</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5998887566777964</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>45.87179636955261</v>
+        <v>87.75858187675476</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5020893562381507</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.942240838910085</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5998887566777964</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>80.76652526855469</v>
+        <v>182.5361700057983</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4289905192472201</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.942240838910085</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5998887566777964</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>87.75858187675476</v>
+        <v>0.3363256454467773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>80.89347428382811</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>32.98778734697751</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>182.5361700057983</v>
+        <v>0.6418373584747314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>80.89347428382811</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>32.98778734697751</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.121366262435913</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>87.75858187675476</v>
+        <v>0.3363256454467773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>80.89347428382811</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>32.98778734697751</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>182.5361700057983</v>
+        <v>0.6418373584747314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>80.89347428382811</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>32.98778734697751</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.121366262435913</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3363256454467773</v>
+        <v>35.55732083320618</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.5811946043919515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.6046477401790427</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>111.88830113121</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>68.50656765299343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6418373584747314</v>
+        <v>63.2348096370697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.591339866408126</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.6046477401790427</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>111.88830113121</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>68.50656765299343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.121366262435913</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3363256454467773</v>
+        <v>35.55732083320618</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.5811946043919515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.6046477401790427</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>111.88830113121</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>68.50656765299343</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6418373584747314</v>
+        <v>63.2348096370697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.591339866408126</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.6046477401790427</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>111.88830113121</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>68.50656765299343</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.121366262435913</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.55732083320618</v>
+        <v>0.3465464115142822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5811946043919515</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>111.88830113121</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>68.50656765299343</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>63.2348096370697</v>
+        <v>0.6315338611602783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.591339866408126</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>111.88830113121</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>68.50656765299343</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.137473344802856</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.55732083320618</v>
+        <v>0.3465464115142822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5811946043919515</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>111.88830113121</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>68.50656765299343</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>63.2348096370697</v>
+        <v>0.6315338611602783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.591339866408126</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>111.88830113121</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>68.50656765299343</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.137473344802856</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3465464115142822</v>
+        <v>106.9222595691681</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6315338611602783</v>
+        <v>180.7806396484375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.137473344802856</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3465464115142822</v>
+        <v>106.9222595691681</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6315338611602783</v>
+        <v>180.7806396484375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>32.98778734697751</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.137473344802856</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>106.9222595691681</v>
+        <v>342.1860818862915</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.8782810451903668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="G2" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="H2" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>180.7806396484375</v>
+        <v>794.1601617336273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.882429566993066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="G3" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="H3" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>106.9222595691681</v>
+        <v>342.1860818862915</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.8782810451903668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="G2" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="H2" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>180.7806396484375</v>
+        <v>794.1601617336273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.882429566993066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="G3" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="H3" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>342.1860818862915</v>
+        <v>80.29093623161316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8782810451903668</v>
+        <v>0.3812621241616503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="G2" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="H2" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>794.1601617336273</v>
+        <v>184.3960673809052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.882429566993066</v>
+        <v>0.3962985813470993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="G3" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="H3" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>342.1860818862915</v>
+        <v>80.29093623161316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8782810451903668</v>
+        <v>0.3812621241616503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="G2" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="H2" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>794.1601617336273</v>
+        <v>184.3960673809052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.882429566993066</v>
+        <v>0.3962985813470993</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="G3" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="H3" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>80.29093623161316</v>
+        <v>0.3484153747558594</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3812621241616503</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4035728160022128</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6796446363370173</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5177601079262396</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>184.3960673809052</v>
+        <v>0.6380558013916016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3962985813470993</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4035728160022128</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6796446363370173</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5177601079262396</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.115167617797852</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>80.29093623161316</v>
+        <v>0.3484153747558594</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3812621241616503</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4035728160022128</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6796446363370173</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5177601079262396</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>184.3960673809052</v>
+        <v>0.6380558013916016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3962985813470993</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4035728160022128</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6796446363370173</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5177601079262396</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.115167617797852</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3484153747558594</v>
+        <v>0.4444608688354492</v>
       </c>
       <c r="E2" t="n">
         <v>0.9493173645748553</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6380558013916016</v>
+        <v>0.9594523906707764</v>
       </c>
       <c r="E3" t="n">
         <v>0.9593934708973952</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.115167617797852</v>
+        <v>1.632286787033081</v>
       </c>
       <c r="E4" t="n">
         <v>0.9663252049059585</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3484153747558594</v>
+        <v>0.4444608688354492</v>
       </c>
       <c r="E2" t="n">
         <v>0.9493173645748553</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6380558013916016</v>
+        <v>0.9594523906707764</v>
       </c>
       <c r="E3" t="n">
         <v>0.9593934708973952</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1.115167617797852</v>
+        <v>1.632286787033081</v>
       </c>
       <c r="E4" t="n">
         <v>0.9663252049059585</v>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4444608688354492</v>
+        <v>89.69519591331482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.5849552540587489</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9594523906707764</v>
+        <v>183.6354990005493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.5863769503374059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.632286787033081</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4444608688354492</v>
+        <v>89.69519591331482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.5849552540587489</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G2" t="n">
-        <v>2.945175805228017</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933262226803274</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9594523906707764</v>
+        <v>183.6354990005493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.5863769503374059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G3" t="n">
-        <v>2.945175805228017</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H3" t="n">
-        <v>1.933262226803274</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.632286787033081</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9663252049059585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9776640607919219</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.945175805228017</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.933262226803274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>89.69519591331482</v>
+        <v>0.4465219974517822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5849552540587489</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.572752040575516</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>87.17635191701446</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>54.04575955422463</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>183.6354990005493</v>
+        <v>1.043767213821411</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5863769503374059</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.572752040575516</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>87.17635191701446</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>54.04575955422463</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.757725715637207</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>89.69519591331482</v>
+        <v>0.4465219974517822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5849552540587489</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.572752040575516</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G2" t="n">
-        <v>87.17635191701446</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H2" t="n">
-        <v>54.04575955422463</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>183.6354990005493</v>
+        <v>1.043767213821411</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5863769503374059</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.572752040575516</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G3" t="n">
-        <v>87.17635191701446</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H3" t="n">
-        <v>54.04575955422463</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.757725715637207</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.933262226803274</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
